--- a/maintenance/TowerAlignment_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/TowerAlignment_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,26 @@
           <t>Tracking_Mode_norm</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -623,6 +643,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -707,6 +739,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -791,6 +835,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -875,6 +931,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -959,6 +1027,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1043,6 +1123,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1127,6 +1219,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resin line seals; Resin line cleaning solvent</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1211,6 +1319,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1295,6 +1415,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1379,6 +1511,18 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1468,6 +1612,18 @@
         <is>
           <t>calendar</t>
         </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6-Month</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/maintenance/TowerAlignment_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/TowerAlignment_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,21 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -599,9 +614,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -625,25 +637,25 @@
           <t>Work at height precautions. Prevent plumb line contacting equipment. Do not disturb established datum positions.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -654,6 +666,15 @@
       </c>
       <c r="Z2" t="n">
         <v>20</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="3">
@@ -695,9 +716,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -721,25 +739,25 @@
           <t>Keep tension pulley retracted to protect load cell; avoid plumb bob collision with capstan.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U3" t="n">
+        <v>93</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -750,6 +768,15 @@
       </c>
       <c r="Z3" t="n">
         <v>20</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="4">
@@ -791,9 +818,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -817,25 +841,25 @@
           <t>Do not disturb gauge once centred; can be used later to quickly re-set pin chuck X/Y for future checks.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U4" t="n">
+        <v>93</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -846,6 +870,15 @@
       </c>
       <c r="Z4" t="n">
         <v>60</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="5">
@@ -887,9 +920,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -913,25 +943,25 @@
           <t>Ensure clamps are re-tightened after adjustment; keep fingers clear of pneumatic mechanisms.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U5" t="n">
+        <v>93</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -942,6 +972,15 @@
       </c>
       <c r="Z5" t="n">
         <v>60</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="6">
@@ -983,9 +1022,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -1009,25 +1045,25 @@
           <t>Use caution with pinch hazards; ensure pressure is reduced/controlled during alignment.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U6" t="n">
+        <v>93</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -1038,6 +1074,15 @@
       </c>
       <c r="Z6" t="n">
         <v>60</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="7">
@@ -1079,9 +1124,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -1105,25 +1147,25 @@
           <t>Restore pressure on low-pressure belt after alignment; keep hands clear of belt nip points.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U7" t="n">
+        <v>93</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -1134,6 +1176,15 @@
       </c>
       <c r="Z7" t="n">
         <v>60</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="8">
@@ -1175,9 +1226,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -1201,19 +1249,20 @@
           <t>Ensure line is through central aperture (not resin feed apertures). Avoid contaminating resin interfaces.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U8" t="n">
+        <v>93</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>event</t>
@@ -1234,6 +1283,15 @@
       </c>
       <c r="Z8" t="n">
         <v>60</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="9">
@@ -1275,9 +1333,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -1301,25 +1356,25 @@
           <t>Laser safety: avoid eye exposure; refit covers after adjustment.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U9" t="n">
+        <v>93</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -1330,6 +1385,15 @@
       </c>
       <c r="Z9" t="n">
         <v>60</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="10">
@@ -1371,9 +1435,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -1397,25 +1458,25 @@
           <t>UV hazard: ensure lamp is off during mechanical alignment; follow lockout procedure.</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U10" t="n">
+        <v>93</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -1426,6 +1487,15 @@
       </c>
       <c r="Z10" t="n">
         <v>60</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="11">
@@ -1467,9 +1537,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Fibre Draw Tower Alignment Manual</t>
@@ -1493,25 +1560,25 @@
           <t>Once centred, avoid moving gauge head; re-check after any mechanical disturbance.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U11" t="n">
+        <v>93</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -1522,6 +1589,15 @@
       </c>
       <c r="Z11" t="n">
         <v>60</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="12">
@@ -1563,7 +1639,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>months</t>
@@ -1595,25 +1670,19 @@
           <t>This is a best-practice interval; adjust based on your tower stability and frequency of equipment moves.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
+          <t>2025-10-13</t>
+        </is>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>calendar</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>6-Month</t>
